--- a/VerveStacks_GBR/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_GBR/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC494D6E-B3CA-4356-BCA3-1AA909F7DB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4026DED1-C28A-4570-98C0-E6B53357BBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1021,7 +1021,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37C74FDA-B3B7-4436-A724-28114F1E85EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FAE4077-A3BB-4793-8979-BDF3965253C2}">
   <dimension ref="B9:L79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_GBR/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_GBR/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE543655-B4C0-48FF-AC48-A6685E3FA6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC1A55FA-535E-4D9E-9B58-84DEB6A9F1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1021,7 +1021,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6078D927-9881-4162-A442-5054F0F0DA7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21271F4B-B49C-4040-856A-3776FB9BFBB2}">
   <dimension ref="B9:L79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4266,28 +4266,28 @@
         <v>133</v>
       </c>
       <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>18</v>
+      </c>
+      <c r="E11">
         <v>8</v>
       </c>
-      <c r="D11">
-        <v>12</v>
-      </c>
-      <c r="E11">
-        <v>5</v>
-      </c>
       <c r="F11">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H11">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.45">
@@ -4346,11 +4346,11 @@
       </c>
       <c r="F20">
         <f>C11</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <f>D11</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -4376,11 +4376,11 @@
       </c>
       <c r="F21">
         <f>E11</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G21">
         <f>F11</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -4406,11 +4406,11 @@
       </c>
       <c r="F22">
         <f>G11</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G22">
         <f>H11</f>
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -4436,11 +4436,11 @@
       </c>
       <c r="F23">
         <f>I11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23">
         <f>J11</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23">
         <v>4</v>
@@ -12041,7 +12041,7 @@
         <v>60</v>
       </c>
       <c r="D542">
-        <v>13060</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.45">
@@ -12055,7 +12055,7 @@
         <v>60</v>
       </c>
       <c r="D543">
-        <v>13345</v>
+        <v>13.345000000000001</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.45">
@@ -12069,7 +12069,7 @@
         <v>60</v>
       </c>
       <c r="D544">
-        <v>13870.338</v>
+        <v>13.870338</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.45">
@@ -12083,7 +12083,7 @@
         <v>60</v>
       </c>
       <c r="D545">
-        <v>14260.91</v>
+        <v>14.260909999999999</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.45">
@@ -12097,7 +12097,7 @@
         <v>60</v>
       </c>
       <c r="D546">
-        <v>14980.769</v>
+        <v>14.980769</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.45">
@@ -12111,7 +12111,7 @@
         <v>60</v>
       </c>
       <c r="D547">
-        <v>16275.263000000001</v>
+        <v>16.275263000000002</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.45">
@@ -12125,7 +12125,7 @@
         <v>60</v>
       </c>
       <c r="D548">
-        <v>17603.079000000002</v>
+        <v>17.603079000000001</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.45">
@@ -12139,7 +12139,7 @@
         <v>60</v>
       </c>
       <c r="D549">
-        <v>1000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
@@ -12153,7 +12153,7 @@
         <v>60</v>
       </c>
       <c r="D550">
-        <v>1753</v>
+        <v>1.7529999999999999</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.45">
@@ -12167,7 +12167,7 @@
         <v>60</v>
       </c>
       <c r="D551">
-        <v>2937</v>
+        <v>2.9369999999999998</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.45">
@@ -12181,7 +12181,7 @@
         <v>60</v>
       </c>
       <c r="D552">
-        <v>5528</v>
+        <v>5.5279999999999996</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.45">
@@ -12195,7 +12195,7 @@
         <v>60</v>
       </c>
       <c r="D553">
-        <v>9601</v>
+        <v>9.6010000000000009</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.45">
@@ -12209,7 +12209,7 @@
         <v>60</v>
       </c>
       <c r="D554">
-        <v>11914</v>
+        <v>11.914</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.45">
@@ -12223,7 +12223,7 @@
         <v>60</v>
       </c>
       <c r="D555">
-        <v>12750.96</v>
+        <v>12.750959999999999</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.45">
@@ -12237,7 +12237,7 @@
         <v>60</v>
       </c>
       <c r="D556">
-        <v>8</v>
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.45">
@@ -12251,7 +12251,7 @@
         <v>60</v>
       </c>
       <c r="D557">
-        <v>11</v>
+        <v>1.0999999999999999E-2</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.45">
@@ -12265,7 +12265,7 @@
         <v>60</v>
       </c>
       <c r="D558">
-        <v>14</v>
+        <v>1.4E-2</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
@@ -12279,7 +12279,7 @@
         <v>60</v>
       </c>
       <c r="D559">
-        <v>18</v>
+        <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.45">
@@ -12293,7 +12293,7 @@
         <v>60</v>
       </c>
       <c r="D560">
-        <v>23</v>
+        <v>2.3E-2</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.45">
@@ -12307,7 +12307,7 @@
         <v>60</v>
       </c>
       <c r="D561">
-        <v>27</v>
+        <v>2.7E-2</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.45">
@@ -12321,7 +12321,7 @@
         <v>60</v>
       </c>
       <c r="D562">
-        <v>95</v>
+        <v>9.5000000000000001E-2</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.45">
@@ -12335,7 +12335,7 @@
         <v>60</v>
       </c>
       <c r="D563">
-        <v>2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.45">
@@ -12349,7 +12349,7 @@
         <v>60</v>
       </c>
       <c r="D564">
-        <v>3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.45">
@@ -12363,7 +12363,7 @@
         <v>60</v>
       </c>
       <c r="D565">
-        <v>4</v>
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.45">
@@ -12377,7 +12377,7 @@
         <v>60</v>
       </c>
       <c r="D566">
-        <v>6</v>
+        <v>6.0000000000000001E-3</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.45">
@@ -12391,7 +12391,7 @@
         <v>59</v>
       </c>
       <c r="D567">
-        <v>3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
@@ -12405,7 +12405,7 @@
         <v>59</v>
       </c>
       <c r="D568">
-        <v>3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.45">
@@ -12419,7 +12419,7 @@
         <v>59</v>
       </c>
       <c r="D569">
-        <v>4</v>
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.45">
@@ -12433,7 +12433,7 @@
         <v>59</v>
       </c>
       <c r="D570">
-        <v>8</v>
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.45">
@@ -12447,7 +12447,7 @@
         <v>59</v>
       </c>
       <c r="D571">
-        <v>11</v>
+        <v>1.0999999999999999E-2</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.45">
@@ -12461,7 +12461,7 @@
         <v>59</v>
       </c>
       <c r="D572">
-        <v>14</v>
+        <v>1.4E-2</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.45">
@@ -12475,7 +12475,7 @@
         <v>59</v>
       </c>
       <c r="D573">
-        <v>17</v>
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.45">
@@ -12489,7 +12489,7 @@
         <v>59</v>
       </c>
       <c r="D574">
-        <v>20</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.45">
@@ -12503,7 +12503,7 @@
         <v>59</v>
       </c>
       <c r="D575">
-        <v>40</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.45">
@@ -12517,7 +12517,7 @@
         <v>59</v>
       </c>
       <c r="D576">
-        <v>244</v>
+        <v>0.24399999999999999</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
@@ -12531,7 +12531,7 @@
         <v>59</v>
       </c>
       <c r="D577">
-        <v>1354</v>
+        <v>1.3540000000000001</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.45">
@@ -12545,7 +12545,7 @@
         <v>59</v>
       </c>
       <c r="D578">
-        <v>2010</v>
+        <v>2.0099999999999998</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.45">
@@ -12559,7 +12559,7 @@
         <v>59</v>
       </c>
       <c r="D579">
-        <v>4054</v>
+        <v>4.0540000000000003</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.45">
@@ -12573,7 +12573,7 @@
         <v>59</v>
       </c>
       <c r="D580">
-        <v>7533</v>
+        <v>7.5330000000000004</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.45">
@@ -12587,7 +12587,7 @@
         <v>59</v>
       </c>
       <c r="D581">
-        <v>10395</v>
+        <v>10.395</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.45">
@@ -12601,7 +12601,7 @@
         <v>59</v>
       </c>
       <c r="D582">
-        <v>11457.268</v>
+        <v>11.457268000000001</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.45">
@@ -12615,7 +12615,7 @@
         <v>59</v>
       </c>
       <c r="D583">
-        <v>12668.39</v>
+        <v>12.668389999999999</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.45">
@@ -12629,7 +12629,7 @@
         <v>59</v>
       </c>
       <c r="D584">
-        <v>12418.06</v>
+        <v>12.418059999999999</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.45">
@@ -12643,7 +12643,7 @@
         <v>59</v>
       </c>
       <c r="D585">
-        <v>12503.986999999999</v>
+        <v>12.503986999999999</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
@@ -12657,7 +12657,7 @@
         <v>59</v>
       </c>
       <c r="D586">
-        <v>12075.493</v>
+        <v>12.075493</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.45">
@@ -12671,7 +12671,7 @@
         <v>59</v>
       </c>
       <c r="D587">
-        <v>13282.906000000001</v>
+        <v>13.282906000000001</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.45">
@@ -12685,7 +12685,7 @@
         <v>59</v>
       </c>
       <c r="D588">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.45">
@@ -12699,7 +12699,7 @@
         <v>59</v>
       </c>
       <c r="D589">
-        <v>2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.45">
@@ -12713,7 +12713,7 @@
         <v>60</v>
       </c>
       <c r="D590">
-        <v>13425.148999999999</v>
+        <v>13.425148999999999</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.45">
@@ -12727,7 +12727,7 @@
         <v>60</v>
       </c>
       <c r="D591">
-        <v>13998.819</v>
+        <v>13.998818999999999</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.45">
@@ -12741,7 +12741,7 @@
         <v>60</v>
       </c>
       <c r="D592">
-        <v>14075.075999999999</v>
+        <v>14.075075999999999</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.45">
@@ -12755,7 +12755,7 @@
         <v>60</v>
       </c>
       <c r="D593">
-        <v>14492.754999999999</v>
+        <v>14.492754999999999</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.45">
@@ -12769,7 +12769,7 @@
         <v>60</v>
       </c>
       <c r="D594">
-        <v>14833.807000000001</v>
+        <v>14.833807</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
@@ -12783,7 +12783,7 @@
         <v>60</v>
       </c>
       <c r="D595">
-        <v>15417.873</v>
+        <v>15.417873</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.45">
@@ -12797,7 +12797,7 @@
         <v>60</v>
       </c>
       <c r="D596">
-        <v>16156.873</v>
+        <v>16.156873000000001</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.45">
@@ -12811,7 +12811,7 @@
         <v>60</v>
       </c>
       <c r="D597">
-        <v>4758</v>
+        <v>4.758</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.45">
@@ -12825,7 +12825,7 @@
         <v>60</v>
       </c>
       <c r="D598">
-        <v>6035</v>
+        <v>6.0350000000000001</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.45">
@@ -12839,7 +12839,7 @@
         <v>60</v>
       </c>
       <c r="D599">
-        <v>7586</v>
+        <v>7.5860000000000003</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.45">
@@ -12853,7 +12853,7 @@
         <v>60</v>
       </c>
       <c r="D600">
-        <v>8573</v>
+        <v>8.5730000000000004</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.45">
@@ -12867,7 +12867,7 @@
         <v>60</v>
       </c>
       <c r="D601">
-        <v>9212</v>
+        <v>9.2119999999999997</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.45">
@@ -12881,7 +12881,7 @@
         <v>60</v>
       </c>
       <c r="D602">
-        <v>10833</v>
+        <v>10.833</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.45">
@@ -12895,7 +12895,7 @@
         <v>60</v>
       </c>
       <c r="D603">
-        <v>12597</v>
+        <v>12.597</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
@@ -12909,7 +12909,7 @@
         <v>60</v>
       </c>
       <c r="D604">
-        <v>809</v>
+        <v>0.80900000000000005</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.45">
@@ -12923,7 +12923,7 @@
         <v>60</v>
       </c>
       <c r="D605">
-        <v>1351</v>
+        <v>1.351</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.45">
@@ -12937,7 +12937,7 @@
         <v>60</v>
       </c>
       <c r="D606">
-        <v>1651</v>
+        <v>1.651</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.45">
@@ -12951,7 +12951,7 @@
         <v>60</v>
       </c>
       <c r="D607">
-        <v>2083</v>
+        <v>2.0830000000000002</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.45">
@@ -12965,7 +12965,7 @@
         <v>60</v>
       </c>
       <c r="D608">
-        <v>2849.8</v>
+        <v>2.8498000000000001</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.45">
@@ -12979,7 +12979,7 @@
         <v>60</v>
       </c>
       <c r="D609">
-        <v>3468</v>
+        <v>3.468</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.45">
@@ -12993,7 +12993,7 @@
         <v>60</v>
       </c>
       <c r="D610">
-        <v>4080</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.45">
@@ -13007,7 +13007,7 @@
         <v>60</v>
       </c>
       <c r="D611">
-        <v>431</v>
+        <v>0.43099999999999999</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.45">
@@ -13021,7 +13021,7 @@
         <v>60</v>
       </c>
       <c r="D612">
-        <v>490</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
@@ -13035,7 +13035,7 @@
         <v>60</v>
       </c>
       <c r="D613">
-        <v>531</v>
+        <v>0.53100000000000003</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.45">
@@ -13049,7 +13049,7 @@
         <v>60</v>
       </c>
       <c r="D614">
-        <v>678</v>
+        <v>0.67800000000000005</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.45">
@@ -13063,7 +13063,7 @@
         <v>59</v>
       </c>
       <c r="D615">
-        <v>1251</v>
+        <v>1.2509999999999999</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.45">
@@ -13077,7 +13077,7 @@
         <v>59</v>
       </c>
       <c r="D616">
-        <v>1275</v>
+        <v>1.2749999999999999</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.45">
@@ -13091,7 +13091,7 @@
         <v>59</v>
       </c>
       <c r="D617">
-        <v>1736</v>
+        <v>1.736</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.45">
@@ -13105,7 +13105,7 @@
         <v>59</v>
       </c>
       <c r="D618">
-        <v>2501</v>
+        <v>2.5009999999999999</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.45">
@@ -13119,7 +13119,7 @@
         <v>59</v>
       </c>
       <c r="D619">
-        <v>3574</v>
+        <v>3.5739999999999998</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.45">
@@ -13133,7 +13133,7 @@
         <v>59</v>
       </c>
       <c r="D620">
-        <v>4491</v>
+        <v>4.4909999999999997</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.45">
@@ -13147,7 +13147,7 @@
         <v>59</v>
       </c>
       <c r="D621">
-        <v>6061</v>
+        <v>6.0609999999999999</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
@@ -13161,7 +13161,7 @@
         <v>59</v>
       </c>
       <c r="D622">
-        <v>7830</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.45">
@@ -13175,7 +13175,7 @@
         <v>59</v>
       </c>
       <c r="D623">
-        <v>7226.33</v>
+        <v>7.2263299999999999</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.45">
@@ -13189,7 +13189,7 @@
         <v>59</v>
       </c>
       <c r="D624">
-        <v>10813.97</v>
+        <v>10.813969999999999</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.45">
@@ -13203,7 +13203,7 @@
         <v>59</v>
       </c>
       <c r="D625">
-        <v>12243.83</v>
+        <v>12.243829999999999</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.45">
@@ -13217,7 +13217,7 @@
         <v>59</v>
       </c>
       <c r="D626">
-        <v>16925.22</v>
+        <v>16.925219999999999</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.45">
@@ -13231,7 +13231,7 @@
         <v>59</v>
       </c>
       <c r="D627">
-        <v>18554.41</v>
+        <v>18.554410000000001</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.45">
@@ -13245,7 +13245,7 @@
         <v>59</v>
       </c>
       <c r="D628">
-        <v>22852.26</v>
+        <v>22.852259999999998</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.45">
@@ -13259,7 +13259,7 @@
         <v>59</v>
       </c>
       <c r="D629">
-        <v>20753.259999999998</v>
+        <v>20.753259999999997</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.45">
@@ -13273,7 +13273,7 @@
         <v>59</v>
       </c>
       <c r="D630">
-        <v>28725.202000000001</v>
+        <v>28.725201999999999</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
@@ -13287,7 +13287,7 @@
         <v>59</v>
       </c>
       <c r="D631">
-        <v>30382.415000000001</v>
+        <v>30.382415000000002</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.45">
@@ -13301,7 +13301,7 @@
         <v>59</v>
       </c>
       <c r="D632">
-        <v>31859.746999999999</v>
+        <v>31.859746999999999</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.45">
@@ -13315,7 +13315,7 @@
         <v>59</v>
       </c>
       <c r="D633">
-        <v>34698.777000000002</v>
+        <v>34.698777</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.45">
@@ -13329,7 +13329,7 @@
         <v>59</v>
       </c>
       <c r="D634">
-        <v>29153.599999999999</v>
+        <v>29.153599999999997</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.45">
@@ -13343,7 +13343,7 @@
         <v>59</v>
       </c>
       <c r="D635">
-        <v>35237.394</v>
+        <v>35.237394000000002</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.45">
@@ -13357,7 +13357,7 @@
         <v>59</v>
       </c>
       <c r="D636">
-        <v>946</v>
+        <v>0.94599999999999995</v>
       </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.45">
@@ -13371,7 +13371,7 @@
         <v>59</v>
       </c>
       <c r="D637">
-        <v>960</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.45">
@@ -13385,7 +13385,7 @@
         <v>60</v>
       </c>
       <c r="D638">
-        <v>8180.5</v>
+        <v>8.1805000000000003</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.45">
@@ -13399,7 +13399,7 @@
         <v>60</v>
       </c>
       <c r="D639">
-        <v>9888.1</v>
+        <v>9.8880999999999997</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
@@ -13413,7 +13413,7 @@
         <v>60</v>
       </c>
       <c r="D640">
-        <v>10382.85</v>
+        <v>10.382850000000001</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.45">
@@ -13427,7 +13427,7 @@
         <v>60</v>
       </c>
       <c r="D641">
-        <v>11255.475</v>
+        <v>11.255475000000001</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.45">
@@ -13441,7 +13441,7 @@
         <v>60</v>
       </c>
       <c r="D642">
-        <v>13927.475</v>
+        <v>13.927475000000001</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.45">
@@ -13455,7 +13455,7 @@
         <v>60</v>
       </c>
       <c r="D643">
-        <v>14745.075000000001</v>
+        <v>14.745075</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.45">
@@ -13469,7 +13469,7 @@
         <v>60</v>
       </c>
       <c r="D644">
-        <v>14745.075000000001</v>
+        <v>14.745075</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.45">
@@ -13483,7 +13483,7 @@
         <v>60</v>
       </c>
       <c r="D645">
-        <v>1838</v>
+        <v>1.8380000000000001</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.45">
@@ -13497,7 +13497,7 @@
         <v>60</v>
       </c>
       <c r="D646">
-        <v>2995</v>
+        <v>2.9950000000000001</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.45">
@@ -13511,7 +13511,7 @@
         <v>60</v>
       </c>
       <c r="D647">
-        <v>3696</v>
+        <v>3.6960000000000002</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.45">
@@ -13525,7 +13525,7 @@
         <v>60</v>
       </c>
       <c r="D648">
-        <v>4501</v>
+        <v>4.5010000000000003</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
@@ -13539,7 +13539,7 @@
         <v>60</v>
       </c>
       <c r="D649">
-        <v>5093</v>
+        <v>5.093</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.45">
@@ -13553,7 +13553,7 @@
         <v>60</v>
       </c>
       <c r="D650">
-        <v>5293</v>
+        <v>5.2930000000000001</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.45">
@@ -13567,7 +13567,7 @@
         <v>60</v>
       </c>
       <c r="D651">
-        <v>6988</v>
+        <v>6.9880000000000004</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.45">
@@ -13581,7 +13581,7 @@
         <v>60</v>
       </c>
       <c r="D652">
-        <v>124</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.45">
@@ -13595,7 +13595,7 @@
         <v>60</v>
       </c>
       <c r="D653">
-        <v>214</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.45">
@@ -13609,7 +13609,7 @@
         <v>60</v>
       </c>
       <c r="D654">
-        <v>304</v>
+        <v>0.30399999999999999</v>
       </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.45">
@@ -13623,7 +13623,7 @@
         <v>60</v>
       </c>
       <c r="D655">
-        <v>394</v>
+        <v>0.39400000000000002</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.45">
@@ -13637,7 +13637,7 @@
         <v>60</v>
       </c>
       <c r="D656">
-        <v>596.20000000000005</v>
+        <v>0.59620000000000006</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.45">
@@ -13651,7 +13651,7 @@
         <v>60</v>
       </c>
       <c r="D657">
-        <v>951</v>
+        <v>0.95099999999999996</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.45">
@@ -13665,7 +13665,7 @@
         <v>60</v>
       </c>
       <c r="D658">
-        <v>1341</v>
+        <v>1.341</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.45">
@@ -13679,7 +13679,7 @@
         <v>60</v>
       </c>
       <c r="D659">
-        <v>4</v>
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.45">
@@ -13693,7 +13693,7 @@
         <v>60</v>
       </c>
       <c r="D660">
-        <v>4</v>
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.45">
@@ -13707,7 +13707,7 @@
         <v>60</v>
       </c>
       <c r="D661">
-        <v>4</v>
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.45">
@@ -13721,7 +13721,7 @@
         <v>60</v>
       </c>
       <c r="D662">
-        <v>64</v>
+        <v>6.4000000000000001E-2</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.45">
@@ -13735,7 +13735,7 @@
         <v>59</v>
       </c>
       <c r="D663">
-        <v>5</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.45">
@@ -13749,7 +13749,7 @@
         <v>59</v>
       </c>
       <c r="D664">
-        <v>10</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.45">
@@ -13763,7 +13763,7 @@
         <v>59</v>
       </c>
       <c r="D665">
-        <v>199</v>
+        <v>0.19900000000000001</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.45">
@@ -13777,7 +13777,7 @@
         <v>59</v>
       </c>
       <c r="D666">
-        <v>403</v>
+        <v>0.40300000000000002</v>
       </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.45">
@@ -13791,7 +13791,7 @@
         <v>59</v>
       </c>
       <c r="D667">
-        <v>651</v>
+        <v>0.65100000000000002</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.45">
@@ -13805,7 +13805,7 @@
         <v>59</v>
       </c>
       <c r="D668">
-        <v>783</v>
+        <v>0.78300000000000003</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.45">
@@ -13819,7 +13819,7 @@
         <v>59</v>
       </c>
       <c r="D669">
-        <v>1335</v>
+        <v>1.335</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.45">
@@ -13833,7 +13833,7 @@
         <v>59</v>
       </c>
       <c r="D670">
-        <v>1754</v>
+        <v>1.754</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.45">
@@ -13847,7 +13847,7 @@
         <v>59</v>
       </c>
       <c r="D671">
-        <v>3059.67</v>
+        <v>3.0596700000000001</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.45">
@@ -13861,7 +13861,7 @@
         <v>59</v>
       </c>
       <c r="D672">
-        <v>5149.03</v>
+        <v>5.1490299999999998</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.45">
@@ -13875,7 +13875,7 @@
         <v>59</v>
       </c>
       <c r="D673">
-        <v>7603.17</v>
+        <v>7.6031700000000004</v>
       </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.45">
@@ -13889,7 +13889,7 @@
         <v>59</v>
       </c>
       <c r="D674">
-        <v>11471.78</v>
+        <v>11.471780000000001</v>
       </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.45">
@@ -13903,7 +13903,7 @@
         <v>59</v>
       </c>
       <c r="D675">
-        <v>13404.59</v>
+        <v>13.404590000000001</v>
       </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.45">
@@ -13917,7 +13917,7 @@
         <v>59</v>
       </c>
       <c r="D676">
-        <v>17422.740000000002</v>
+        <v>17.422740000000001</v>
       </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.45">
@@ -13931,7 +13931,7 @@
         <v>59</v>
       </c>
       <c r="D677">
-        <v>16405.740000000002</v>
+        <v>16.405740000000002</v>
       </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.45">
@@ -13945,7 +13945,7 @@
         <v>59</v>
       </c>
       <c r="D678">
-        <v>20915.919999999998</v>
+        <v>20.91592</v>
       </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.45">
@@ -13959,7 +13959,7 @@
         <v>59</v>
       </c>
       <c r="D679">
-        <v>26525.200000000001</v>
+        <v>26.525200000000002</v>
       </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.45">
@@ -13973,7 +13973,7 @@
         <v>59</v>
       </c>
       <c r="D680">
-        <v>31975.15</v>
+        <v>31.975150000000003</v>
       </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.45">
@@ -13987,7 +13987,7 @@
         <v>59</v>
       </c>
       <c r="D681">
-        <v>40681.089999999997</v>
+        <v>40.681089999999998</v>
       </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.45">
@@ -14001,7 +14001,7 @@
         <v>59</v>
       </c>
       <c r="D682">
-        <v>35509.54</v>
+        <v>35.509540000000001</v>
       </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.45">
@@ -14015,7 +14015,7 @@
         <v>59</v>
       </c>
       <c r="D683">
-        <v>45019.87</v>
+        <v>45.019870000000004</v>
       </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.45">
@@ -14029,7 +14029,7 @@
         <v>59</v>
       </c>
       <c r="D684">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.45">
@@ -14043,7 +14043,7 @@
         <v>59</v>
       </c>
       <c r="D685">
-        <v>5</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.45">

--- a/VerveStacks_GBR/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_GBR/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC1A55FA-535E-4D9E-9B58-84DEB6A9F1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5BBEBDE-8A5B-41B2-8FEB-1C3749C3E787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1021,7 +1021,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21271F4B-B49C-4040-856A-3776FB9BFBB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50ED8BA1-6765-4223-9E54-6EC35BDF6DE1}">
   <dimension ref="B9:L79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
